--- a/docs/pdf-to-svg/PdfToSvg_仕様一覧.xlsx
+++ b/docs/pdf-to-svg/PdfToSvg_仕様一覧.xlsx
@@ -19,9 +19,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'入出力定義'!$A$4:$E$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'入出力定義'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'入出力定義'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RPC・HTTP'!$A$4:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RPC・HTTP'!$A$4:$D$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'RPC・HTTP'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'RPC・HTTP'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'RPC・HTTP'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'テスト仕様'!$A$4:$E$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'テスト仕様'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'テスト仕様'!$A$1:$E$15</definedName>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>dictList / dictAdd</t>
+          <t>dictList / dictAdd / dictDelete</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>辞書参照 / 追加</t>
+          <t>辞書 参照 / 追加 / 削除</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>setOnlyHeaders</t>
+          <t>reapplyDict / reapplyDictPage</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>ヘッダのみ適用フラグ更新</t>
+          <t>辞書の全ファイル / 単一ページ再適用</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,137 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
+          <t>dictExport / dictImport</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>辞書JSONのファイル書き出し / 読み込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>dictJson / dictImportJson</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>辞書JSONの文字列受け渡し</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>setOnlyHeaders</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>ヘッダのみ適用フラグ更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>applyDelete / deleteRegion / addBorder</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>削除 / 範囲削除 / 枠線（Undoへpush）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>undo / redo</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>操作の取消 / やり直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
           <t>exportSvg</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>範囲指定で SVG 書き出し</t>
         </is>
       </c>
     </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>removeFile</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>選択ファイルを一覧から除去</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D16"/>
+  <autoFilter ref="A4:D22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
